--- a/WIp/Silly zombie game.xlsx
+++ b/WIp/Silly zombie game.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\WIp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6005FD0-53D4-4DA3-82CA-96B2D2F6BF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBB6C50-99C1-4277-8683-67256D76D650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="594" firstSheet="3" activeTab="7" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" firstSheet="6" activeTab="6" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="607">
   <si>
     <t>Line1</t>
   </si>
@@ -1663,10 +1663,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Foraging Hut</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lumber Camp</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2065,112 +2061,114 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Single Story Building</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multi Story Building</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TF\Resources:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Community Garden</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military Surplus Store</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industrial Warehouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commercial Zone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parking Lot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Granary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aquaculture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abandoned Evac Site</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Church</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hunts</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cabin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medicinal Herbs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Books</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Library</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bookstore</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Watertower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water Purification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recreation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Materials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Perishable Food</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Warehouse</t>
+  </si>
+  <si>
+    <t>Single Story Building</t>
+  </si>
+  <si>
     <t>Weaponry</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fuel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Single Story Building</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Multi Story Building</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TF\Resources:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Community Garden</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Military Surplus Store</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Industrial Warehouse</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Commercial Zone</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Parking Lot</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Granary</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aquaculture</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Abandoned Evac Site</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Church</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hunts</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cabin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Medicinal Herbs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Books</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Library</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bookstore</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Water</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Watertower</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Water Purification</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Perishable Food</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recreation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Camp</t>
   </si>
 </sst>
 </file>
@@ -2501,7 +2499,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2697,6 +2695,24 @@
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2704,30 +2720,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3045,42 +3037,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="23.875" style="3"/>
+    <col min="1" max="16384" width="23.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65" t="s">
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65" t="s">
-        <v>562</v>
-      </c>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65" t="s">
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71" t="s">
+        <v>561</v>
+      </c>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-    </row>
-    <row r="2" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+    </row>
+    <row r="2" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>78</v>
       </c>
@@ -3133,22 +3125,22 @@
         <v>16</v>
       </c>
       <c r="R2" s="28" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>3</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H3" s="30"/>
       <c r="I3" s="30"/>
@@ -3166,7 +3158,7 @@
       <c r="Q3" s="34"/>
       <c r="R3" s="34"/>
     </row>
-    <row r="4" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>4</v>
       </c>
@@ -3175,17 +3167,17 @@
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="30" t="s">
+        <v>557</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>558</v>
       </c>
-      <c r="E4" s="30" t="s">
-        <v>559</v>
-      </c>
       <c r="F4" s="30" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G4" s="30"/>
       <c r="H4" s="30" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>44</v>
@@ -3204,17 +3196,17 @@
       <c r="O4" s="31"/>
       <c r="P4" s="34"/>
       <c r="Q4" s="33" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="R4" s="34"/>
     </row>
-    <row r="5" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>5</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="30"/>
@@ -3228,7 +3220,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L5" s="32"/>
       <c r="M5" s="31"/>
@@ -3244,14 +3236,14 @@
       <c r="Q5" s="34"/>
       <c r="R5" s="34"/>
     </row>
-    <row r="6" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
         <v>6</v>
       </c>
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="35" t="s">
@@ -3259,14 +3251,14 @@
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="36" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I6" s="36"/>
       <c r="J6" s="36" t="s">
         <v>37</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L6" s="37"/>
       <c r="M6" s="31" t="s">
@@ -3278,7 +3270,7 @@
       <c r="Q6" s="34"/>
       <c r="R6" s="34"/>
     </row>
-    <row r="7" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>189</v>
       </c>
@@ -3294,11 +3286,11 @@
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="35" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H7" s="36"/>
       <c r="I7" s="36" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -3311,16 +3303,16 @@
       </c>
       <c r="O7" s="31"/>
       <c r="P7" s="33" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q7" s="33" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="R7" s="33" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28">
         <v>8</v>
       </c>
@@ -3337,7 +3329,7 @@
       </c>
       <c r="I8" s="38"/>
       <c r="J8" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K8" s="40"/>
       <c r="L8" s="32"/>
@@ -3352,7 +3344,7 @@
       <c r="Q8" s="34"/>
       <c r="R8" s="34"/>
     </row>
-    <row r="9" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>9</v>
       </c>
@@ -3360,7 +3352,7 @@
       <c r="C9" s="38"/>
       <c r="D9" s="38"/>
       <c r="E9" s="38" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F9" s="38"/>
       <c r="G9" s="38" t="s">
@@ -3388,7 +3380,7 @@
       <c r="Q9" s="34"/>
       <c r="R9" s="34"/>
     </row>
-    <row r="10" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>10</v>
       </c>
@@ -3396,14 +3388,14 @@
         <v>190</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D10" s="38" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="38" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
@@ -3412,11 +3404,11 @@
       <c r="I10" s="38"/>
       <c r="J10" s="41"/>
       <c r="K10" s="40" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L10" s="32"/>
       <c r="M10" s="40" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N10" s="40"/>
       <c r="O10" s="40" t="s">
@@ -3424,11 +3416,11 @@
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="33" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R10" s="34"/>
     </row>
-    <row r="11" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>11</v>
       </c>
@@ -3447,7 +3439,7 @@
         <v>38</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K11" s="40"/>
       <c r="L11" s="32"/>
@@ -3458,7 +3450,7 @@
       <c r="Q11" s="34"/>
       <c r="R11" s="34"/>
     </row>
-    <row r="12" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
@@ -3478,7 +3470,7 @@
       <c r="Q12" s="42"/>
       <c r="R12" s="42"/>
     </row>
-    <row r="13" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
       <c r="B13" s="43" t="s">
         <v>195</v>
@@ -3530,9 +3522,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>447</v>
       </c>
@@ -3554,7 +3546,7 @@
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>205</v>
       </c>
@@ -3571,7 +3563,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>448</v>
       </c>
@@ -3621,7 +3613,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>205</v>
       </c>
@@ -3662,7 +3654,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>453</v>
       </c>
@@ -3670,7 +3662,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
@@ -3684,73 +3676,73 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>247</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>202</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>249</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>323</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -3763,12 +3755,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="31.625" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>255</v>
       </c>
@@ -3792,7 +3784,7 @@
       </c>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>256</v>
       </c>
@@ -3806,17 +3798,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65E430D-86E9-43E2-AFAF-E995519B62A8}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="23.125" style="50"/>
+    <col min="1" max="16384" width="23.109375" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="50" t="s">
         <v>421</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D1" s="50" t="s">
         <v>422</v>
@@ -3843,7 +3835,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
         <v>78</v>
       </c>
@@ -3857,25 +3849,25 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="72" t="s">
         <v>282</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
       <c r="J3" s="50" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>1</v>
       </c>
@@ -3889,7 +3881,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>2</v>
       </c>
@@ -3903,7 +3895,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="51" t="s">
         <v>3</v>
       </c>
@@ -3923,7 +3915,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="s">
         <v>4</v>
       </c>
@@ -3937,7 +3929,7 @@
         <v>288</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I7" s="50" t="s">
         <v>308</v>
@@ -3946,24 +3938,24 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D8" s="50" t="s">
         <v>279</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I8" s="50" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="s">
         <v>6</v>
       </c>
@@ -3980,12 +3972,12 @@
         <v>317</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="51" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F10" s="50" t="s">
         <v>309</v>
@@ -3994,74 +3986,74 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="51" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="51" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="51" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="51" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="51" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="51"/>
     </row>
-    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="51"/>
     </row>
-    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="51"/>
     </row>
-    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="51"/>
     </row>
-    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="51"/>
     </row>
-    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="52"/>
     </row>
-    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="52"/>
     </row>
-    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="52"/>
     </row>
-    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="52"/>
     </row>
-    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="52"/>
     </row>
   </sheetData>
@@ -4077,13 +4069,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.875" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="19.875" style="2"/>
+    <col min="1" max="1" width="19.88671875" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="19.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50"/>
       <c r="B1" s="50" t="s">
         <v>193</v>
@@ -4122,7 +4114,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
         <v>95</v>
       </c>
@@ -4155,19 +4147,19 @@
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
     </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>494</v>
-      </c>
-      <c r="B3" s="66" t="s">
+        <v>493</v>
+      </c>
+      <c r="B3" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
       <c r="I3" s="50" t="s">
         <v>301</v>
       </c>
@@ -4178,7 +4170,7 @@
       </c>
       <c r="M3" s="50"/>
     </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
         <v>80</v>
       </c>
@@ -4197,7 +4189,7 @@
       <c r="L4" s="50"/>
       <c r="M4" s="50"/>
     </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
         <v>25</v>
       </c>
@@ -4216,7 +4208,7 @@
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
     </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
         <v>19</v>
       </c>
@@ -4225,7 +4217,7 @@
         <v>210</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="50" t="s">
@@ -4241,7 +4233,7 @@
       </c>
       <c r="M6" s="50"/>
     </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56" t="s">
         <v>81</v>
       </c>
@@ -4266,26 +4258,26 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
       <c r="I8" s="50"/>
       <c r="J8" s="50"/>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
     </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
         <v>82</v>
       </c>
@@ -4312,7 +4304,7 @@
       </c>
       <c r="M9" s="50"/>
     </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
         <v>83</v>
       </c>
@@ -4333,7 +4325,7 @@
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
     </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
         <v>26</v>
       </c>
@@ -4358,7 +4350,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56" t="s">
         <v>27</v>
       </c>
@@ -4381,7 +4373,7 @@
       </c>
       <c r="M12" s="50"/>
     </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57" t="s">
         <v>87</v>
       </c>
@@ -4402,7 +4394,7 @@
       <c r="L13" s="50"/>
       <c r="M13" s="50"/>
     </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56" t="s">
         <v>32</v>
       </c>
@@ -4427,7 +4419,7 @@
       </c>
       <c r="M14" s="50"/>
     </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57" t="s">
         <v>84</v>
       </c>
@@ -4446,7 +4438,7 @@
       </c>
       <c r="M15" s="50"/>
     </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56" t="s">
         <v>38</v>
       </c>
@@ -4469,7 +4461,7 @@
       <c r="L16" s="50"/>
       <c r="M16" s="50"/>
     </row>
-    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="57" t="s">
         <v>85</v>
       </c>
@@ -4492,7 +4484,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58" t="s">
         <v>42</v>
       </c>
@@ -4525,7 +4517,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>86</v>
       </c>
@@ -4548,7 +4540,7 @@
       <c r="L19" s="50"/>
       <c r="M19" s="50"/>
     </row>
-    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="s">
         <v>88</v>
       </c>
@@ -4569,7 +4561,7 @@
       </c>
       <c r="M20" s="50"/>
     </row>
-    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>43</v>
       </c>
@@ -4594,7 +4586,7 @@
       <c r="L21" s="50"/>
       <c r="M21" s="50"/>
     </row>
-    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58" t="s">
         <v>39</v>
       </c>
@@ -4617,7 +4609,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>89</v>
       </c>
@@ -4642,7 +4634,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>90</v>
       </c>
@@ -4663,7 +4655,7 @@
       </c>
       <c r="M24" s="50"/>
     </row>
-    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="59" t="s">
         <v>91</v>
       </c>
@@ -4688,7 +4680,7 @@
       </c>
       <c r="M25" s="50"/>
     </row>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>71</v>
       </c>
@@ -4707,7 +4699,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60" t="s">
         <v>92</v>
       </c>
@@ -4730,7 +4722,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60" t="s">
         <v>72</v>
       </c>
@@ -4762,9 +4754,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
         <v>344</v>
       </c>
@@ -4773,7 +4765,7 @@
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="62"/>
       <c r="B2" s="62" t="s">
         <v>346</v>
@@ -4784,7 +4776,7 @@
       <c r="D2" s="62"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
         <v>345</v>
       </c>
@@ -4795,7 +4787,7 @@
       <c r="D3" s="62"/>
       <c r="E3" s="20"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="62"/>
       <c r="B4" s="62" t="s">
         <v>349</v>
@@ -4806,7 +4798,7 @@
       <c r="D4" s="62"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="62"/>
       <c r="B5" s="62"/>
       <c r="C5" s="62" t="s">
@@ -4815,7 +4807,7 @@
       <c r="D5" s="62"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="63"/>
       <c r="B6" s="63" t="s">
         <v>352</v>
@@ -4828,7 +4820,7 @@
       </c>
       <c r="E6" s="63"/>
     </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="63" t="s">
         <v>355</v>
       </c>
@@ -4845,7 +4837,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="63"/>
       <c r="B8" s="63" t="s">
         <v>360</v>
@@ -4858,7 +4850,7 @@
       </c>
       <c r="E8" s="63"/>
     </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="63"/>
       <c r="B9" s="63" t="s">
         <v>363</v>
@@ -4871,7 +4863,7 @@
       </c>
       <c r="E9" s="63"/>
     </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63"/>
       <c r="B10" s="63" t="s">
         <v>366</v>
@@ -4884,7 +4876,7 @@
       </c>
       <c r="E10" s="63"/>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="63"/>
       <c r="B11" s="63" t="s">
         <v>369</v>
@@ -4897,7 +4889,7 @@
       </c>
       <c r="E11" s="63"/>
     </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="64" t="s">
         <v>372</v>
       </c>
@@ -4914,7 +4906,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
       <c r="B13" s="64" t="s">
         <v>377</v>
@@ -4925,7 +4917,7 @@
       <c r="D13" s="64"/>
       <c r="E13" s="64"/>
     </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
         <v>379</v>
       </c>
@@ -4940,7 +4932,7 @@
       </c>
       <c r="E14" s="64"/>
     </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64"/>
       <c r="B15" s="64" t="s">
         <v>383</v>
@@ -4951,7 +4943,7 @@
       <c r="D15" s="64"/>
       <c r="E15" s="64"/>
     </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
         <v>385</v>
       </c>
@@ -4962,7 +4954,7 @@
       <c r="D16" s="64"/>
       <c r="E16" s="64"/>
     </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="64"/>
       <c r="B17" s="64" t="s">
         <v>391</v>
@@ -4973,7 +4965,7 @@
       <c r="D17" s="64"/>
       <c r="E17" s="64"/>
     </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
         <v>386</v>
       </c>
@@ -4984,7 +4976,7 @@
       <c r="D18" s="64"/>
       <c r="E18" s="64"/>
     </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="64"/>
       <c r="B19" s="64" t="s">
         <v>393</v>
@@ -4999,7 +4991,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="64"/>
       <c r="B20" s="64" t="s">
         <v>394</v>
@@ -5010,7 +5002,7 @@
       <c r="D20" s="64"/>
       <c r="E20" s="64"/>
     </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
         <v>387</v>
       </c>
@@ -5025,7 +5017,7 @@
       </c>
       <c r="E21" s="64"/>
     </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="64" t="s">
         <v>388</v>
       </c>
@@ -5038,7 +5030,7 @@
       <c r="D22" s="64"/>
       <c r="E22" s="64"/>
     </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="64"/>
       <c r="B23" s="64" t="s">
         <v>397</v>
@@ -5051,12 +5043,12 @@
       </c>
       <c r="E23" s="64"/>
     </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="64" t="s">
         <v>389</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C24" s="64" t="s">
         <v>407</v>
@@ -5068,101 +5060,101 @@
         <v>409</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="64" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="64" t="s">
+        <v>531</v>
+      </c>
+      <c r="C25" s="64" t="s">
         <v>532</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="D25" s="64" t="s">
         <v>533</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="E25" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="E25" s="64" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
     </row>
-    <row r="28" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
     </row>
-    <row r="29" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
     </row>
-    <row r="30" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
     </row>
-    <row r="31" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
     </row>
-    <row r="32" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
     </row>
-    <row r="33" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
     </row>
-    <row r="34" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
     </row>
-    <row r="35" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
     </row>
-    <row r="36" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
     </row>
-    <row r="37" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
     </row>
-    <row r="38" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -5178,41 +5170,41 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="16" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>555</v>
-      </c>
-      <c r="B1" s="67" t="s">
+        <v>554</v>
+      </c>
+      <c r="B1" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67" t="s">
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-    </row>
-    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+    </row>
+    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19"/>
       <c r="B2" s="21" t="s">
         <v>48</v>
@@ -5245,7 +5237,7 @@
         <v>56</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>63</v>
@@ -5263,7 +5255,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
       <c r="B3" s="19" t="s">
         <v>137</v>
@@ -5278,10 +5270,10 @@
         <v>148</v>
       </c>
       <c r="F3" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>520</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>521</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>147</v>
@@ -5305,7 +5297,7 @@
         <v>170</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="P3" s="19" t="s">
         <v>177</v>
@@ -5314,7 +5306,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -5329,7 +5321,7 @@
         <v>149</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>335</v>
@@ -5347,7 +5339,7 @@
         <v>165</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M4" s="19" t="s">
         <v>171</v>
@@ -5359,13 +5351,13 @@
         <v>176</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Q4" s="19" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26"/>
       <c r="B5" s="19" t="s">
         <v>138</v>
@@ -5377,7 +5369,7 @@
         <v>136</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>150</v>
@@ -5389,7 +5381,7 @@
         <v>332</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>159</v>
@@ -5398,25 +5390,25 @@
         <v>166</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="M5" s="19" t="s">
         <v>172</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="O5" s="19" t="s">
         <v>178</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q5" s="19" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26"/>
       <c r="B6" s="19" t="s">
         <v>139</v>
@@ -5428,16 +5420,16 @@
         <v>145</v>
       </c>
       <c r="E6" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="F6" s="19" t="s">
         <v>518</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>519</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I6" s="19" t="s">
         <v>156</v>
@@ -5467,7 +5459,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26"/>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -5481,7 +5473,7 @@
         <v>151</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H7" s="19" t="s">
         <v>155</v>
@@ -5500,13 +5492,13 @@
         <v>180</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="Q7" s="19" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26"/>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -5525,7 +5517,7 @@
       <c r="P8" s="26"/>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26"/>
       <c r="B9" s="21" t="s">
         <v>64</v>
@@ -5570,12 +5562,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="20.75" style="9"/>
+    <col min="1" max="16384" width="20.77734375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="11" t="s">
         <v>411</v>
       </c>
@@ -5595,11 +5587,11 @@
         <v>416</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>205</v>
       </c>
@@ -5625,7 +5617,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>131</v>
       </c>
@@ -5648,7 +5640,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>125</v>
       </c>
@@ -5674,7 +5666,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>327</v>
       </c>
@@ -5685,19 +5677,19 @@
         <v>417</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>417</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -5709,9 +5701,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDA60A-2197-46FF-A1E9-DE6B49F4104C}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="4" t="s">
         <v>466</v>
@@ -5723,33 +5715,33 @@
         <v>468</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>205</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>450</v>
@@ -5761,24 +5753,24 @@
         <v>450</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>476</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>477</v>
       </c>
       <c r="I2" s="14" t="s">
         <v>253</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>131</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>271</v>
@@ -5787,27 +5779,27 @@
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="14" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
     </row>
-    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>491</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>492</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -5820,61 +5812,61 @@
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="16" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>410</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E7" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>473</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>474</v>
-      </c>
       <c r="H7" s="16" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
     </row>
-    <row r="8" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>484</v>
-      </c>
       <c r="D8" s="13" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E8" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>479</v>
-      </c>
       <c r="H8" s="13" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -5888,314 +5880,314 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF92F2CA-29A6-4C2C-9AA2-481D5812D9FC}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="29.375" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="29.33203125" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="29.375" style="29"/>
+    <col min="1" max="16384" width="29.33203125" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>564</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>580</v>
+      </c>
+      <c r="C1" s="69" t="s">
+        <v>601</v>
+      </c>
+      <c r="D1" s="69" t="s">
+        <v>602</v>
+      </c>
+      <c r="E1" s="69" t="s">
+        <v>600</v>
+      </c>
+      <c r="F1" s="70" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1" s="70" t="s">
+        <v>599</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>605</v>
+      </c>
+      <c r="I1" s="68" t="s">
+        <v>251</v>
+      </c>
+      <c r="J1" s="68" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="65" t="s">
         <v>565</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>583</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>603</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>600</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>605</v>
-      </c>
-      <c r="F1" s="75" t="s">
-        <v>597</v>
-      </c>
-      <c r="G1" s="75" t="s">
-        <v>604</v>
-      </c>
-      <c r="H1" s="73" t="s">
-        <v>579</v>
-      </c>
-      <c r="I1" s="73" t="s">
-        <v>580</v>
-      </c>
-      <c r="J1" s="73" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
-        <v>566</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>576</v>
+      <c r="B2" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>590</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>576</v>
+        <v>587</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>414</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="G2" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="I2" s="29" t="s">
         <v>576</v>
       </c>
-      <c r="G2" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="H2" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="I2" s="70" t="s">
-        <v>577</v>
-      </c>
-      <c r="J2" s="71" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>567</v>
-      </c>
-      <c r="B3" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>576</v>
+      <c r="J2" s="66" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>566</v>
+      </c>
+      <c r="B3" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="F3" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="G3" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="H3" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="I3" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="J3" s="71" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
-        <v>568</v>
-      </c>
-      <c r="B4" s="70" t="s">
-        <v>581</v>
-      </c>
-      <c r="C4" s="70" t="s">
-        <v>571</v>
-      </c>
-      <c r="D4" s="71" t="s">
-        <v>576</v>
+      <c r="E3" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="F3" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="G3" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="I3" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="J3" s="66" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="65" t="s">
+        <v>567</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>578</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="D4" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>116</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>599</v>
-      </c>
-      <c r="G4" s="68" t="s">
+        <v>596</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>590</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>465</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>585</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>586</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>597</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>582</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="J5" s="66" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="29" t="s">
+        <v>573</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>591</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>592</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="J6" s="67" t="s">
         <v>593</v>
       </c>
-      <c r="H4" s="70" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="65" t="s">
+        <v>568</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>604</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>588</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>598</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>584</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>596</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>423</v>
+      </c>
+      <c r="H7" s="29" t="s">
         <v>465</v>
       </c>
-      <c r="I4" s="70" t="s">
-        <v>588</v>
-      </c>
-      <c r="J4" s="70" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="70" t="s">
+      <c r="I7" s="29" t="s">
+        <v>585</v>
+      </c>
+      <c r="J7" s="66" t="s">
         <v>575</v>
       </c>
-      <c r="C5" s="70" t="s">
-        <v>589</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>601</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>586</v>
-      </c>
-      <c r="F5" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="G5" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="H5" s="70" t="s">
-        <v>585</v>
-      </c>
-      <c r="I5" s="70" t="s">
-        <v>572</v>
-      </c>
-      <c r="J5" s="71" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="29" t="s">
-        <v>574</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>594</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="E6" s="68" t="s">
-        <v>595</v>
-      </c>
-      <c r="F6" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="G6" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="H6" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="I6" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="J6" s="72" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="69" t="s">
-        <v>569</v>
-      </c>
-      <c r="B7" s="70" t="s">
-        <v>581</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>591</v>
-      </c>
-      <c r="D7" s="68" t="s">
-        <v>602</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>587</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>599</v>
-      </c>
-      <c r="G7" s="70" t="s">
-        <v>423</v>
-      </c>
-      <c r="H7" s="70" t="s">
-        <v>465</v>
-      </c>
-      <c r="I7" s="70" t="s">
-        <v>588</v>
-      </c>
-      <c r="J7" s="71" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="70" t="s">
-        <v>582</v>
+    </row>
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="29" t="s">
+        <v>579</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="71" t="s">
-        <v>576</v>
+      <c r="D8" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>117</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>584</v>
-      </c>
-      <c r="H8" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="I8" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="J8" s="70" t="s">
+        <v>581</v>
+      </c>
+      <c r="H8" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="I8" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="J8" s="29" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="70" t="s">
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="29" t="s">
+        <v>574</v>
+      </c>
+      <c r="C9" s="66" t="s">
         <v>575</v>
       </c>
-      <c r="C9" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="D9" s="71" t="s">
-        <v>576</v>
+      <c r="D9" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>586</v>
-      </c>
-      <c r="F9" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="G9" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="H9" s="70" t="s">
+        <v>583</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="G9" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="H9" s="29" t="s">
         <v>465</v>
       </c>
-      <c r="I9" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="J9" s="71" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="69" t="s">
-        <v>570</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="C10" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="D10" s="71" t="s">
-        <v>576</v>
+      <c r="I9" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="J9" s="66" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="65" t="s">
+        <v>569</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="D10" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>573</v>
-      </c>
-      <c r="F10" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="G10" s="71" t="s">
-        <v>576</v>
+        <v>572</v>
+      </c>
+      <c r="F10" s="66" t="s">
+        <v>575</v>
+      </c>
+      <c r="G10" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>592</v>
-      </c>
-      <c r="I10" s="71" t="s">
-        <v>576</v>
+        <v>589</v>
+      </c>
+      <c r="I10" s="66" t="s">
+        <v>575</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>119</v>
@@ -6210,9 +6202,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>462</v>
       </c>
@@ -6241,7 +6233,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>205</v>
       </c>
@@ -6270,7 +6262,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>131</v>
       </c>
@@ -6290,7 +6282,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -6319,7 +6311,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>327</v>
       </c>
@@ -6348,7 +6340,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>250</v>
       </c>
@@ -6365,7 +6357,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>463</v>
       </c>
@@ -6382,7 +6374,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>251</v>
       </c>
@@ -6396,7 +6388,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>126</v>
       </c>
@@ -6410,7 +6402,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>329</v>
       </c>
@@ -6424,7 +6416,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>464</v>
       </c>
@@ -6438,7 +6430,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>120</v>
       </c>
@@ -6449,12 +6441,12 @@
         <v>458</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>127</v>
       </c>
@@ -6465,7 +6457,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>328</v>
       </c>

--- a/WIp/Silly zombie game.xlsx
+++ b/WIp/Silly zombie game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\WIp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBB6C50-99C1-4277-8683-67256D76D650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7530EC10-7C3B-4880-B5D1-F38F8E6A8999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" firstSheet="6" activeTab="6" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" activeTab="3" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="608">
   <si>
     <t>Line1</t>
   </si>
@@ -2169,6 +2169,9 @@
   </si>
   <si>
     <t>Camp</t>
+  </si>
+  <si>
+    <t>Strength</t>
   </si>
 </sst>
 </file>
@@ -4068,14 +4071,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="2" customWidth="1"/>
     <col min="2" max="16384" width="19.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50"/>
       <c r="B1" s="50" t="s">
         <v>193</v>
@@ -4113,8 +4116,11 @@
       <c r="M1" s="50" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
         <v>95</v>
       </c>
@@ -4146,8 +4152,11 @@
       <c r="K2" s="50"/>
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
-    </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
         <v>493</v>
       </c>
@@ -4170,7 +4179,7 @@
       </c>
       <c r="M3" s="50"/>
     </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
         <v>80</v>
       </c>
@@ -4188,8 +4197,11 @@
       <c r="K4" s="50"/>
       <c r="L4" s="50"/>
       <c r="M4" s="50"/>
-    </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
         <v>25</v>
       </c>
@@ -4208,7 +4220,7 @@
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
     </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
         <v>19</v>
       </c>
@@ -4233,7 +4245,7 @@
       </c>
       <c r="M6" s="50"/>
     </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56" t="s">
         <v>81</v>
       </c>
@@ -4258,7 +4270,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
         <v>20</v>
       </c>
@@ -4277,7 +4289,7 @@
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
     </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
         <v>82</v>
       </c>
@@ -4304,7 +4316,7 @@
       </c>
       <c r="M9" s="50"/>
     </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
         <v>83</v>
       </c>
@@ -4325,7 +4337,7 @@
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
     </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
         <v>26</v>
       </c>
@@ -4350,7 +4362,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56" t="s">
         <v>27</v>
       </c>
@@ -4373,7 +4385,7 @@
       </c>
       <c r="M12" s="50"/>
     </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57" t="s">
         <v>87</v>
       </c>
@@ -4394,7 +4406,7 @@
       <c r="L13" s="50"/>
       <c r="M13" s="50"/>
     </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56" t="s">
         <v>32</v>
       </c>
@@ -4419,7 +4431,7 @@
       </c>
       <c r="M14" s="50"/>
     </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57" t="s">
         <v>84</v>
       </c>
@@ -4438,7 +4450,7 @@
       </c>
       <c r="M15" s="50"/>
     </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56" t="s">
         <v>38</v>
       </c>

--- a/WIp/Silly zombie game.xlsx
+++ b/WIp/Silly zombie game.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\WIp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7530EC10-7C3B-4880-B5D1-F38F8E6A8999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672ECC8E-E71F-40FA-A9B6-9995E6C841C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" activeTab="3" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" activeTab="1" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
     <sheet name="Building Sheets" sheetId="9" r:id="rId2"/>
-    <sheet name="Unit Sheets" sheetId="4" r:id="rId3"/>
-    <sheet name="Promotion" sheetId="10" r:id="rId4"/>
-    <sheet name="Policy Tree" sheetId="3" r:id="rId5"/>
-    <sheet name="Locations(Wonder)" sheetId="11" r:id="rId6"/>
-    <sheet name="Improvements" sheetId="14" r:id="rId7"/>
-    <sheet name="Locations(RES) (2)" sheetId="15" r:id="rId8"/>
-    <sheet name="Locations(RES)" sheetId="5" r:id="rId9"/>
-    <sheet name="Terrain" sheetId="13" r:id="rId10"/>
-    <sheet name="C.Mechanics" sheetId="6" r:id="rId11"/>
-    <sheet name="U.Mechanics" sheetId="8" r:id="rId12"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId3"/>
+    <sheet name="Unit Sheets" sheetId="4" r:id="rId4"/>
+    <sheet name="Promotion" sheetId="10" r:id="rId5"/>
+    <sheet name="Policy Tree" sheetId="3" r:id="rId6"/>
+    <sheet name="Locations(Wonder)" sheetId="11" r:id="rId7"/>
+    <sheet name="Improvements" sheetId="14" r:id="rId8"/>
+    <sheet name="Locations(RES) (2)" sheetId="15" r:id="rId9"/>
+    <sheet name="Locations(RES)" sheetId="5" r:id="rId10"/>
+    <sheet name="Terrain" sheetId="13" r:id="rId11"/>
+    <sheet name="C.Mechanics" sheetId="6" r:id="rId12"/>
+    <sheet name="U.Mechanics" sheetId="8" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="620">
   <si>
     <t>Line1</t>
   </si>
@@ -2172,6 +2173,42 @@
   </si>
   <si>
     <t>Strength</t>
+  </si>
+  <si>
+    <t>Zombie Risk meter</t>
+  </si>
+  <si>
+    <t>10% -25%</t>
+  </si>
+  <si>
+    <t>0% -10%</t>
+  </si>
+  <si>
+    <t>25% -50%</t>
+  </si>
+  <si>
+    <t>50% -75%</t>
+  </si>
+  <si>
+    <t>75% -90%</t>
+  </si>
+  <si>
+    <t>Seldom Hordes, Special Infected</t>
+  </si>
+  <si>
+    <t>Often Horde, Seldom SI</t>
+  </si>
+  <si>
+    <t>Both Horde and SI are often</t>
+  </si>
+  <si>
+    <t>Army Attrition</t>
+  </si>
+  <si>
+    <t>Brute become common</t>
+  </si>
+  <si>
+    <t>Very often everything</t>
   </si>
 </sst>
 </file>
@@ -2502,7 +2539,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2724,6 +2761,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3523,6 +3566,281 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" t="s">
+        <v>459</v>
+      </c>
+      <c r="E3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+      <c r="E5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G5" t="s">
+        <v>330</v>
+      </c>
+      <c r="H5" t="s">
+        <v>329</v>
+      </c>
+      <c r="I5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>463</v>
+      </c>
+      <c r="B8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>464</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>425</v>
+      </c>
+      <c r="D14" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" t="s">
+        <v>424</v>
+      </c>
+      <c r="D17" t="s">
+        <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
   <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3668,85 +3986,6 @@
     <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>504</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3756,6 +3995,85 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4070,6 +4388,69 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B3A3E0A-1959-4E5D-B6C8-D645C202C4AB}">
+  <dimension ref="B2:C8"/>
+  <sheetFormatPr defaultColWidth="22.5546875" defaultRowHeight="60.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="74" t="s">
+        <v>609</v>
+      </c>
+      <c r="C4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="74" t="s">
+        <v>611</v>
+      </c>
+      <c r="C5" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="74" t="s">
+        <v>612</v>
+      </c>
+      <c r="C6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="74" t="s">
+        <v>613</v>
+      </c>
+      <c r="C7" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="75">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>619</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:N28"/>
   <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4763,7 +5144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
   <dimension ref="A1:E38"/>
   <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5179,7 +5560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5571,7 +5952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5710,7 +6091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDA60A-2197-46FF-A1E9-DE6B49F4104C}">
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5889,7 +6270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF92F2CA-29A6-4C2C-9AA2-481D5812D9FC}">
   <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="29.33203125" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6209,279 +6590,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>462</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D3" t="s">
-        <v>459</v>
-      </c>
-      <c r="E3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E5" t="s">
-        <v>328</v>
-      </c>
-      <c r="F5" t="s">
-        <v>328</v>
-      </c>
-      <c r="G5" t="s">
-        <v>330</v>
-      </c>
-      <c r="H5" t="s">
-        <v>329</v>
-      </c>
-      <c r="I5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>463</v>
-      </c>
-      <c r="B8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E8" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>329</v>
-      </c>
-      <c r="C11" t="s">
-        <v>331</v>
-      </c>
-      <c r="D11" t="s">
-        <v>329</v>
-      </c>
-      <c r="E11" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>464</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" t="s">
-        <v>425</v>
-      </c>
-      <c r="D14" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>328</v>
-      </c>
-      <c r="C17" t="s">
-        <v>424</v>
-      </c>
-      <c r="D17" t="s">
-        <v>424</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/WIp/Silly zombie game.xlsx
+++ b/WIp/Silly zombie game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\WIp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672ECC8E-E71F-40FA-A9B6-9995E6C841C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD6544B-59A8-4FB9-A73D-ACC3E5B696D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" activeTab="1" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" activeTab="4" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="619">
   <si>
     <t>Line1</t>
   </si>
@@ -1354,12 +1354,6 @@
   </si>
   <si>
     <t>Shovel</t>
-  </si>
-  <si>
-    <t>Pike</t>
-  </si>
-  <si>
-    <t>Halberd</t>
   </si>
   <si>
     <t>Javalin</t>
@@ -2209,6 +2203,9 @@
   </si>
   <si>
     <t>Very often everything</t>
+  </si>
+  <si>
+    <t>Polearms</t>
   </si>
 </sst>
 </file>
@@ -2539,7 +2536,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2753,20 +2750,17 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3092,31 +3086,31 @@
       <c r="A1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71" t="s">
-        <v>561</v>
-      </c>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71" t="s">
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73" t="s">
+        <v>559</v>
+      </c>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
     </row>
     <row r="2" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
@@ -3171,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="R2" s="28" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -3180,13 +3174,13 @@
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H3" s="30"/>
       <c r="I3" s="30"/>
@@ -3213,17 +3207,17 @@
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="30" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G4" s="30"/>
       <c r="H4" s="30" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>44</v>
@@ -3242,7 +3236,7 @@
       <c r="O4" s="31"/>
       <c r="P4" s="34"/>
       <c r="Q4" s="33" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="R4" s="34"/>
     </row>
@@ -3252,7 +3246,7 @@
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="30"/>
@@ -3266,7 +3260,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="L5" s="32"/>
       <c r="M5" s="31"/>
@@ -3289,7 +3283,7 @@
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="35" t="s">
@@ -3297,14 +3291,14 @@
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="36" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="I6" s="36"/>
       <c r="J6" s="36" t="s">
         <v>37</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="L6" s="37"/>
       <c r="M6" s="31" t="s">
@@ -3332,11 +3326,11 @@
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="35" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H7" s="36"/>
       <c r="I7" s="36" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -3349,10 +3343,10 @@
       </c>
       <c r="O7" s="31"/>
       <c r="P7" s="33" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q7" s="33" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="R7" s="33" t="s">
         <v>135</v>
@@ -3375,7 +3369,7 @@
       </c>
       <c r="I8" s="38"/>
       <c r="J8" s="39" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K8" s="40"/>
       <c r="L8" s="32"/>
@@ -3398,7 +3392,7 @@
       <c r="C9" s="38"/>
       <c r="D9" s="38"/>
       <c r="E9" s="38" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F9" s="38"/>
       <c r="G9" s="38" t="s">
@@ -3434,14 +3428,14 @@
         <v>190</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D10" s="38" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="38" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
@@ -3450,11 +3444,11 @@
       <c r="I10" s="38"/>
       <c r="J10" s="41"/>
       <c r="K10" s="40" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L10" s="32"/>
       <c r="M10" s="40" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N10" s="40"/>
       <c r="O10" s="40" t="s">
@@ -3462,7 +3456,7 @@
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="33" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="R10" s="34"/>
     </row>
@@ -3485,7 +3479,7 @@
         <v>38</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K11" s="40"/>
       <c r="L11" s="32"/>
@@ -3572,7 +3566,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>116</v>
@@ -3596,7 +3590,7 @@
         <v>118</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3636,7 +3630,7 @@
         <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E3" t="s">
         <v>129</v>
@@ -3711,21 +3705,21 @@
         <v>250</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>119</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B8" t="s">
         <v>252</v>
@@ -3784,13 +3778,13 @@
     </row>
     <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>308</v>
@@ -3801,10 +3795,10 @@
         <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3828,10 +3822,10 @@
         <v>328</v>
       </c>
       <c r="C17" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D17" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -3847,22 +3841,22 @@
   <sheetData>
     <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -3875,63 +3869,63 @@
         <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D2" t="s">
         <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="M4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3939,7 +3933,7 @@
         <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C5" t="s">
         <v>253</v>
@@ -3948,16 +3942,16 @@
         <v>253</v>
       </c>
       <c r="G5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H5" t="s">
         <v>253</v>
       </c>
       <c r="J5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L5" t="s">
         <v>253</v>
@@ -3969,18 +3963,18 @@
         <v>254</v>
       </c>
       <c r="O5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4004,13 +3998,13 @@
         <v>247</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>202</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>203</v>
@@ -4021,13 +4015,13 @@
         <v>248</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>324</v>
@@ -4038,13 +4032,13 @@
         <v>249</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>323</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>325</v>
@@ -4055,15 +4049,15 @@
         <v>246</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -4126,13 +4120,13 @@
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="50" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D1" s="50" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E1" s="50" t="s">
         <v>258</v>
@@ -4250,7 +4244,7 @@
         <v>288</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I7" s="50" t="s">
         <v>308</v>
@@ -4264,13 +4258,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D8" s="50" t="s">
         <v>279</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I8" s="50" t="s">
         <v>314</v>
@@ -4298,7 +4292,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F10" s="50" t="s">
         <v>309</v>
@@ -4394,55 +4388,55 @@
   <sheetData>
     <row r="2" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C3" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>607</v>
+      </c>
+      <c r="C4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C5" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>610</v>
       </c>
-      <c r="C3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
-        <v>609</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="74" t="s">
+    <row r="7" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>611</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
-        <v>612</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="8" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="71">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>617</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
-        <v>613</v>
-      </c>
-      <c r="C7" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="75">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -4498,7 +4492,7 @@
         <v>111</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -4539,7 +4533,7 @@
     </row>
     <row r="3" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B3" s="72" t="s">
         <v>216</v>
@@ -4610,7 +4604,7 @@
         <v>210</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="50" t="s">
@@ -5290,58 +5284,55 @@
         <v>373</v>
       </c>
       <c r="C12" s="64" t="s">
+        <v>618</v>
+      </c>
+      <c r="D12" s="64" t="s">
         <v>374</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>375</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
       <c r="B13" s="64" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D13" s="64"/>
       <c r="E13" s="64"/>
     </row>
     <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
+        <v>377</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>378</v>
+      </c>
+      <c r="C14" s="64" t="s">
         <v>379</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="D14" s="64" t="s">
         <v>380</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>381</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>382</v>
       </c>
       <c r="E14" s="64"/>
     </row>
     <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64"/>
       <c r="B15" s="64" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D15" s="64"/>
       <c r="E15" s="64"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C16" s="64"/>
       <c r="D16" s="64"/>
@@ -5350,20 +5341,20 @@
     <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="64"/>
       <c r="B17" s="64" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D17" s="64"/>
       <c r="E17" s="64"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C18" s="64"/>
       <c r="D18" s="64"/>
@@ -5372,53 +5363,53 @@
     <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="64"/>
       <c r="B19" s="64" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C19" s="64" t="s">
+        <v>397</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>398</v>
+      </c>
+      <c r="E19" s="64" t="s">
         <v>399</v>
-      </c>
-      <c r="D19" s="64" t="s">
-        <v>400</v>
-      </c>
-      <c r="E19" s="64" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="64"/>
       <c r="B20" s="64" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="64"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D21" s="64" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E21" s="64"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="64" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D22" s="64"/>
       <c r="E22" s="64"/>
@@ -5426,31 +5417,31 @@
     <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="64"/>
       <c r="B23" s="64" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D23" s="64" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E23" s="64"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="64" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C24" s="64" t="s">
+        <v>405</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>406</v>
+      </c>
+      <c r="E24" s="64" t="s">
         <v>407</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>408</v>
-      </c>
-      <c r="E24" s="64" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5458,16 +5449,16 @@
         <v>38</v>
       </c>
       <c r="B25" s="64" t="s">
+        <v>529</v>
+      </c>
+      <c r="C25" s="64" t="s">
+        <v>530</v>
+      </c>
+      <c r="D25" s="64" t="s">
         <v>531</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="E25" s="64" t="s">
         <v>532</v>
-      </c>
-      <c r="D25" s="64" t="s">
-        <v>533</v>
-      </c>
-      <c r="E25" s="64" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5570,32 +5561,32 @@
   <sheetData>
     <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>554</v>
-      </c>
-      <c r="B1" s="73" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73" t="s">
+      <c r="C1" s="74"/>
+      <c r="D1" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73" t="s">
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19"/>
@@ -5630,7 +5621,7 @@
         <v>56</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>63</v>
@@ -5663,10 +5654,10 @@
         <v>148</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>147</v>
@@ -5690,7 +5681,7 @@
         <v>170</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P3" s="19" t="s">
         <v>177</v>
@@ -5714,7 +5705,7 @@
         <v>149</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>335</v>
@@ -5732,7 +5723,7 @@
         <v>165</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="M4" s="19" t="s">
         <v>171</v>
@@ -5744,7 +5735,7 @@
         <v>176</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q4" s="19" t="s">
         <v>186</v>
@@ -5762,7 +5753,7 @@
         <v>136</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>150</v>
@@ -5774,7 +5765,7 @@
         <v>332</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>159</v>
@@ -5783,19 +5774,19 @@
         <v>166</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="M5" s="19" t="s">
         <v>172</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="O5" s="19" t="s">
         <v>178</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q5" s="19" t="s">
         <v>187</v>
@@ -5813,16 +5804,16 @@
         <v>145</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="I6" s="19" t="s">
         <v>156</v>
@@ -5866,7 +5857,7 @@
         <v>151</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H7" s="19" t="s">
         <v>155</v>
@@ -5885,7 +5876,7 @@
         <v>180</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Q7" s="19" t="s">
         <v>188</v>
@@ -5962,25 +5953,25 @@
   <sheetData>
     <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>416</v>
-      </c>
       <c r="H1" s="10" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="N1" s="10"/>
     </row>
@@ -5989,25 +5980,25 @@
         <v>205</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>122</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>420</v>
-      </c>
       <c r="H2" s="9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6064,25 +6055,25 @@
         <v>327</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -6099,31 +6090,31 @@
     <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>469</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -6131,31 +6122,31 @@
         <v>205</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>254</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I2" s="14" t="s">
         <v>253</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -6163,7 +6154,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>271</v>
@@ -6172,7 +6163,7 @@
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -6183,10 +6174,10 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="13" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
@@ -6213,50 +6204,50 @@
     <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="16" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D7" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>484</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>473</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>486</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>485</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>477</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -6280,127 +6271,127 @@
   <sheetData>
     <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="65" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D1" s="69" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E1" s="69" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F1" s="70" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G1" s="70" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H1" s="68" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I1" s="68" t="s">
         <v>251</v>
       </c>
       <c r="J1" s="68" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B2" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G2" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H2" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I2" s="29" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="65" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J3" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>116</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>118</v>
@@ -6408,118 +6399,118 @@
     </row>
     <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="29" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G5" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J5" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>589</v>
+      </c>
+      <c r="D6" s="66" t="s">
         <v>573</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="E6" s="29" t="s">
+        <v>590</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>573</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>573</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>573</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>573</v>
+      </c>
+      <c r="J6" s="67" t="s">
         <v>591</v>
-      </c>
-      <c r="D6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>592</v>
-      </c>
-      <c r="F6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="G6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="65" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J7" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="29" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>117</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H8" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I8" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J8" s="29" t="s">
         <v>118</v>
@@ -6527,60 +6518,60 @@
     </row>
     <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="29" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F9" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G9" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I9" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J9" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F10" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G10" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="I10" s="66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>119</v>

--- a/WIp/Silly zombie game.xlsx
+++ b/WIp/Silly zombie game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\WIp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672ECC8E-E71F-40FA-A9B6-9995E6C841C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79D7921-30ED-4915-B76F-022E06D9BBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" activeTab="1" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="594" activeTab="3" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="621">
   <si>
     <t>Line1</t>
   </si>
@@ -1357,9 +1357,6 @@
   </si>
   <si>
     <t>Pike</t>
-  </si>
-  <si>
-    <t>Halberd</t>
   </si>
   <si>
     <t>Javalin</t>
@@ -2209,6 +2206,12 @@
   </si>
   <si>
     <t>Very often everything</t>
+  </si>
+  <si>
+    <t>Melee: Early game small upgrades</t>
+  </si>
+  <si>
+    <t>Archery: Early game ranged upgrades</t>
   </si>
 </sst>
 </file>
@@ -2539,7 +2542,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2753,20 +2756,23 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3092,31 +3098,31 @@
       <c r="A1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71" t="s">
-        <v>561</v>
-      </c>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71" t="s">
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73" t="s">
+        <v>560</v>
+      </c>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
     </row>
     <row r="2" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
@@ -3171,7 +3177,7 @@
         <v>16</v>
       </c>
       <c r="R2" s="28" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -3180,13 +3186,13 @@
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H3" s="30"/>
       <c r="I3" s="30"/>
@@ -3213,17 +3219,17 @@
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="30" t="s">
+        <v>556</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="E4" s="30" t="s">
-        <v>558</v>
-      </c>
       <c r="F4" s="30" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G4" s="30"/>
       <c r="H4" s="30" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>44</v>
@@ -3242,7 +3248,7 @@
       <c r="O4" s="31"/>
       <c r="P4" s="34"/>
       <c r="Q4" s="33" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="R4" s="34"/>
     </row>
@@ -3252,7 +3258,7 @@
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="30"/>
@@ -3266,7 +3272,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L5" s="32"/>
       <c r="M5" s="31"/>
@@ -3289,7 +3295,7 @@
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="35" t="s">
@@ -3297,14 +3303,14 @@
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="36" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I6" s="36"/>
       <c r="J6" s="36" t="s">
         <v>37</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L6" s="37"/>
       <c r="M6" s="31" t="s">
@@ -3332,11 +3338,11 @@
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="35" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H7" s="36"/>
       <c r="I7" s="36" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -3349,10 +3355,10 @@
       </c>
       <c r="O7" s="31"/>
       <c r="P7" s="33" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q7" s="33" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="R7" s="33" t="s">
         <v>135</v>
@@ -3375,7 +3381,7 @@
       </c>
       <c r="I8" s="38"/>
       <c r="J8" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K8" s="40"/>
       <c r="L8" s="32"/>
@@ -3398,7 +3404,7 @@
       <c r="C9" s="38"/>
       <c r="D9" s="38"/>
       <c r="E9" s="38" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F9" s="38"/>
       <c r="G9" s="38" t="s">
@@ -3434,14 +3440,14 @@
         <v>190</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D10" s="38" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
@@ -3450,11 +3456,11 @@
       <c r="I10" s="38"/>
       <c r="J10" s="41"/>
       <c r="K10" s="40" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L10" s="32"/>
       <c r="M10" s="40" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N10" s="40"/>
       <c r="O10" s="40" t="s">
@@ -3462,7 +3468,7 @@
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="33" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="R10" s="34"/>
     </row>
@@ -3485,7 +3491,7 @@
         <v>38</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K11" s="40"/>
       <c r="L11" s="32"/>
@@ -3572,7 +3578,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>116</v>
@@ -3596,7 +3602,7 @@
         <v>118</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3636,7 +3642,7 @@
         <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E3" t="s">
         <v>129</v>
@@ -3711,21 +3717,21 @@
         <v>250</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>119</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B8" t="s">
         <v>252</v>
@@ -3784,13 +3790,13 @@
     </row>
     <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>308</v>
@@ -3801,10 +3807,10 @@
         <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D14" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3828,10 +3834,10 @@
         <v>328</v>
       </c>
       <c r="C17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -3847,22 +3853,22 @@
   <sheetData>
     <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>429</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -3875,63 +3881,63 @@
         <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D2" t="s">
         <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3939,7 +3945,7 @@
         <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C5" t="s">
         <v>253</v>
@@ -3948,16 +3954,16 @@
         <v>253</v>
       </c>
       <c r="G5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H5" t="s">
         <v>253</v>
       </c>
       <c r="J5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L5" t="s">
         <v>253</v>
@@ -3969,18 +3975,18 @@
         <v>254</v>
       </c>
       <c r="O5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4004,13 +4010,13 @@
         <v>247</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>202</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>203</v>
@@ -4021,13 +4027,13 @@
         <v>248</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>324</v>
@@ -4038,13 +4044,13 @@
         <v>249</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>323</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>325</v>
@@ -4055,15 +4061,15 @@
         <v>246</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -4126,13 +4132,13 @@
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="50" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>494</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>422</v>
       </c>
       <c r="E1" s="50" t="s">
         <v>258</v>
@@ -4250,7 +4256,7 @@
         <v>288</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I7" s="50" t="s">
         <v>308</v>
@@ -4264,13 +4270,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D8" s="50" t="s">
         <v>279</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I8" s="50" t="s">
         <v>314</v>
@@ -4298,7 +4304,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F10" s="50" t="s">
         <v>309</v>
@@ -4394,55 +4400,55 @@
   <sheetData>
     <row r="2" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C3" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>610</v>
       </c>
-      <c r="C3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
-        <v>609</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="74" t="s">
+    <row r="6" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>611</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
+    <row r="7" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>612</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
-        <v>613</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="71">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>618</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="75">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -4498,7 +4504,7 @@
         <v>111</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -4539,7 +4545,7 @@
     </row>
     <row r="3" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B3" s="72" t="s">
         <v>216</v>
@@ -4610,7 +4616,7 @@
         <v>210</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="50" t="s">
@@ -5146,10 +5152,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="20.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
         <v>344</v>
       </c>
@@ -5158,7 +5167,7 @@
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="62"/>
       <c r="B2" s="62" t="s">
         <v>346</v>
@@ -5169,7 +5178,7 @@
       <c r="D2" s="62"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
         <v>345</v>
       </c>
@@ -5180,7 +5189,7 @@
       <c r="D3" s="62"/>
       <c r="E3" s="20"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="62"/>
       <c r="B4" s="62" t="s">
         <v>349</v>
@@ -5191,7 +5200,7 @@
       <c r="D4" s="62"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="62"/>
       <c r="B5" s="62"/>
       <c r="C5" s="62" t="s">
@@ -5200,7 +5209,7 @@
       <c r="D5" s="62"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="63"/>
       <c r="B6" s="63" t="s">
         <v>352</v>
@@ -5213,7 +5222,7 @@
       </c>
       <c r="E6" s="63"/>
     </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="63" t="s">
         <v>355</v>
       </c>
@@ -5230,7 +5239,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="63"/>
       <c r="B8" s="63" t="s">
         <v>360</v>
@@ -5243,7 +5252,7 @@
       </c>
       <c r="E8" s="63"/>
     </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="63"/>
       <c r="B9" s="63" t="s">
         <v>363</v>
@@ -5256,7 +5265,7 @@
       </c>
       <c r="E9" s="63"/>
     </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63"/>
       <c r="B10" s="63" t="s">
         <v>366</v>
@@ -5269,7 +5278,7 @@
       </c>
       <c r="E10" s="63"/>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="63"/>
       <c r="B11" s="63" t="s">
         <v>369</v>
@@ -5282,7 +5291,7 @@
       </c>
       <c r="E11" s="63"/>
     </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="64" t="s">
         <v>372</v>
       </c>
@@ -5295,217 +5304,236 @@
       <c r="D12" s="64" t="s">
         <v>375</v>
       </c>
-      <c r="E12" s="64" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="75" t="s">
+        <v>619</v>
+      </c>
+      <c r="I12" s="75"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
       <c r="B13" s="64" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="64" t="s">
         <v>377</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>378</v>
       </c>
       <c r="D13" s="64"/>
       <c r="E13" s="64"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13" s="75" t="s">
+        <v>620</v>
+      </c>
+      <c r="I13" s="75"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14" s="64" t="s">
         <v>379</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="C14" s="64" t="s">
         <v>380</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="D14" s="64" t="s">
         <v>381</v>
       </c>
-      <c r="D14" s="64" t="s">
-        <v>382</v>
-      </c>
       <c r="E14" s="64"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64"/>
       <c r="B15" s="64" t="s">
+        <v>382</v>
+      </c>
+      <c r="C15" s="64" t="s">
         <v>383</v>
-      </c>
-      <c r="C15" s="64" t="s">
-        <v>384</v>
       </c>
       <c r="D15" s="64"/>
       <c r="E15" s="64"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C16" s="64"/>
       <c r="D16" s="64"/>
       <c r="E16" s="64"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="64"/>
       <c r="B17" s="64" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D17" s="64"/>
       <c r="E17" s="64"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C18" s="64"/>
       <c r="D18" s="64"/>
       <c r="E18" s="64"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="76"/>
+      <c r="I18" s="76"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="64"/>
       <c r="B19" s="64" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C19" s="64" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="D19" s="64" t="s">
+      <c r="E19" s="64" t="s">
         <v>400</v>
       </c>
-      <c r="E19" s="64" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="76"/>
+      <c r="I19" s="76"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="64"/>
       <c r="B20" s="64" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="64"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="76"/>
+      <c r="I20" s="76"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
+        <v>386</v>
+      </c>
+      <c r="B21" s="64" t="s">
+        <v>394</v>
+      </c>
+      <c r="C21" s="64" t="s">
+        <v>402</v>
+      </c>
+      <c r="D21" s="64" t="s">
+        <v>403</v>
+      </c>
+      <c r="E21" s="64"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="B21" s="64" t="s">
+      <c r="B22" s="64" t="s">
         <v>395</v>
       </c>
-      <c r="C21" s="64" t="s">
-        <v>403</v>
-      </c>
-      <c r="D21" s="64" t="s">
+      <c r="C22" s="64" t="s">
         <v>404</v>
-      </c>
-      <c r="E21" s="64"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
-        <v>388</v>
-      </c>
-      <c r="B22" s="64" t="s">
-        <v>396</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>405</v>
       </c>
       <c r="D22" s="64"/>
       <c r="E22" s="64"/>
     </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="64"/>
       <c r="B23" s="64" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C23" s="64" t="s">
+        <v>405</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>409</v>
+      </c>
+      <c r="E23" s="64"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B24" s="64" t="s">
+        <v>534</v>
+      </c>
+      <c r="C24" s="64" t="s">
         <v>406</v>
       </c>
-      <c r="D23" s="64" t="s">
-        <v>410</v>
-      </c>
-      <c r="E23" s="64"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
-        <v>389</v>
-      </c>
-      <c r="B24" s="64" t="s">
-        <v>535</v>
-      </c>
-      <c r="C24" s="64" t="s">
+      <c r="D24" s="64" t="s">
         <v>407</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="E24" s="64" t="s">
         <v>408</v>
       </c>
-      <c r="E24" s="64" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="64" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="64" t="s">
+        <v>530</v>
+      </c>
+      <c r="C25" s="64" t="s">
         <v>531</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="D25" s="64" t="s">
         <v>532</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="E25" s="64" t="s">
         <v>533</v>
       </c>
-      <c r="E25" s="64" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
     </row>
-    <row r="28" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
     </row>
-    <row r="29" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
     </row>
-    <row r="30" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
     </row>
-    <row r="31" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
     </row>
-    <row r="32" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -5555,6 +5583,11 @@
       <c r="E38" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5570,32 +5603,32 @@
   <sheetData>
     <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>554</v>
-      </c>
-      <c r="B1" s="73" t="s">
+        <v>553</v>
+      </c>
+      <c r="B1" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73" t="s">
+      <c r="C1" s="74"/>
+      <c r="D1" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73" t="s">
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19"/>
@@ -5630,7 +5663,7 @@
         <v>56</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>63</v>
@@ -5663,10 +5696,10 @@
         <v>148</v>
       </c>
       <c r="F3" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>519</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>520</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>147</v>
@@ -5690,7 +5723,7 @@
         <v>170</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P3" s="19" t="s">
         <v>177</v>
@@ -5714,7 +5747,7 @@
         <v>149</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>335</v>
@@ -5732,7 +5765,7 @@
         <v>165</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M4" s="19" t="s">
         <v>171</v>
@@ -5744,7 +5777,7 @@
         <v>176</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q4" s="19" t="s">
         <v>186</v>
@@ -5762,7 +5795,7 @@
         <v>136</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>150</v>
@@ -5774,7 +5807,7 @@
         <v>332</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>159</v>
@@ -5783,19 +5816,19 @@
         <v>166</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M5" s="19" t="s">
         <v>172</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="O5" s="19" t="s">
         <v>178</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Q5" s="19" t="s">
         <v>187</v>
@@ -5813,16 +5846,16 @@
         <v>145</v>
       </c>
       <c r="E6" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="F6" s="19" t="s">
         <v>517</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>518</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I6" s="19" t="s">
         <v>156</v>
@@ -5866,7 +5899,7 @@
         <v>151</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H7" s="19" t="s">
         <v>155</v>
@@ -5885,7 +5918,7 @@
         <v>180</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q7" s="19" t="s">
         <v>188</v>
@@ -5962,25 +5995,25 @@
   <sheetData>
     <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D1" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>416</v>
-      </c>
       <c r="H1" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N1" s="10"/>
     </row>
@@ -5989,25 +6022,25 @@
         <v>205</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>122</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>420</v>
-      </c>
       <c r="H2" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6064,25 +6097,25 @@
         <v>327</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -6099,31 +6132,31 @@
     <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>470</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -6131,31 +6164,31 @@
         <v>205</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>254</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>475</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>476</v>
       </c>
       <c r="I2" s="14" t="s">
         <v>253</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -6163,7 +6196,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>271</v>
@@ -6172,7 +6205,7 @@
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="14" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -6183,10 +6216,10 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>490</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>491</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
@@ -6213,50 +6246,50 @@
     <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="16" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E7" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>473</v>
-      </c>
       <c r="H7" s="16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>483</v>
-      </c>
       <c r="D8" s="13" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E8" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>478</v>
-      </c>
       <c r="H8" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -6280,127 +6313,127 @@
   <sheetData>
     <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="65" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C1" s="69" t="s">
+        <v>600</v>
+      </c>
+      <c r="D1" s="69" t="s">
         <v>601</v>
       </c>
-      <c r="D1" s="69" t="s">
-        <v>602</v>
-      </c>
       <c r="E1" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F1" s="70" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G1" s="70" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1" s="68" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I1" s="68" t="s">
         <v>251</v>
       </c>
       <c r="J1" s="68" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B2" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>586</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="G2" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="I2" s="29" t="s">
         <v>575</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>587</v>
-      </c>
-      <c r="D2" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>414</v>
-      </c>
-      <c r="F2" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="G2" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="H2" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>576</v>
-      </c>
       <c r="J2" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="65" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J3" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>116</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>118</v>
@@ -6408,118 +6441,118 @@
     </row>
     <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="29" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G5" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J5" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C6" s="67" t="s">
+        <v>590</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="E6" s="29" t="s">
         <v>591</v>
       </c>
-      <c r="D6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="E6" s="29" t="s">
+      <c r="F6" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="J6" s="67" t="s">
         <v>592</v>
-      </c>
-      <c r="F6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="G6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>575</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="65" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E7" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>464</v>
+      </c>
+      <c r="I7" s="29" t="s">
         <v>584</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>596</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>423</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>465</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>585</v>
-      </c>
       <c r="J7" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="29" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>117</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H8" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I8" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J8" s="29" t="s">
         <v>118</v>
@@ -6527,60 +6560,60 @@
     </row>
     <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="29" t="s">
+        <v>573</v>
+      </c>
+      <c r="C9" s="66" t="s">
         <v>574</v>
       </c>
-      <c r="C9" s="66" t="s">
-        <v>575</v>
-      </c>
       <c r="D9" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F9" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G9" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I9" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J9" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F10" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G10" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I10" s="66" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>119</v>
